--- a/data/trans_orig/IP07C14-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C14-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23455</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>21910</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24752</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39713</t>
+          <t>39013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>25625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>24576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41508</t>
+          <t>42030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22409</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38736</t>
+          <t>39052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50706</t>
+          <t>50883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74673</t>
+          <t>73785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31260</t>
+          <t>31433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50072</t>
+          <t>50014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26654</t>
+          <t>27349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43583</t>
+          <t>45232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63526</t>
+          <t>64252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88651</t>
+          <t>89143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>56192</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76401</t>
+          <t>77519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49984</t>
+          <t>50110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70814</t>
+          <t>71093</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111368</t>
+          <t>112435</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141384</t>
+          <t>142121</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26526</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>28393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44739</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66708</t>
+          <t>67139</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26123</t>
+          <t>26240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42867</t>
+          <t>43306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63734</t>
+          <t>64230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73753</t>
+          <t>72297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100560</t>
+          <t>100544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31366</t>
+          <t>31661</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23514</t>
+          <t>23353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22229</t>
+          <t>21856</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37090</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31183</t>
+          <t>30838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50273</t>
+          <t>50092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72323</t>
+          <t>72302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33039</t>
+          <t>33178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>52684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89260</t>
+          <t>87430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118651</t>
+          <t>118267</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>45697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66721</t>
+          <t>66560</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37504</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57913</t>
+          <t>57769</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>86785</t>
+          <t>88796</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>117286</t>
+          <t>117461</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82136</t>
+          <t>82497</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>107090</t>
+          <t>106066</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>80712</t>
+          <t>80025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105459</t>
+          <t>105533</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>169017</t>
+          <t>168323</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>206677</t>
+          <t>203814</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59313</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66390</t>
+          <t>65180</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92731</t>
+          <t>91277</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41273</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>62037</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65491</t>
+          <t>65032</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89669</t>
+          <t>89033</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112950</t>
+          <t>112741</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>145094</t>
+          <t>144704</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26785</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>17498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18546</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32331</t>
+          <t>31981</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29921</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13695</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>26543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41468</t>
+          <t>41595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62639</t>
+          <t>61440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30676</t>
+          <t>30739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48789</t>
+          <t>48315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76853</t>
+          <t>77186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104089</t>
+          <t>105247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>32622</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51330</t>
+          <t>51378</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42916</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63337</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89299</t>
+          <t>88383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41740</t>
+          <t>41842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62588</t>
+          <t>63690</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57010</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79814</t>
+          <t>77000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104290</t>
+          <t>104094</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>135967</t>
+          <t>134354</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35085</t>
+          <t>35659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26916</t>
+          <t>27074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50257</t>
+          <t>51363</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74261</t>
+          <t>74446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21511</t>
+          <t>21232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36762</t>
+          <t>37116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39651</t>
+          <t>39428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59752</t>
+          <t>59469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64888</t>
+          <t>64577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90809</t>
+          <t>91053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34235</t>
+          <t>34427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42671</t>
+          <t>41577</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18162</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>17669</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>17915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33276</t>
+          <t>32124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66065</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90781</t>
+          <t>93830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69129</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>119733</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153041</t>
+          <t>154032</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49377</t>
+          <t>50178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71865</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34085</t>
+          <t>34550</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53278</t>
+          <t>54001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>88489</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>119170</t>
+          <t>119497</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>70243</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96125</t>
+          <t>96293</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81894</t>
+          <t>83259</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107959</t>
+          <t>108346</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>159318</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>199705</t>
+          <t>194896</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>31563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50709</t>
+          <t>51908</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45095</t>
+          <t>45642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69210</t>
+          <t>68929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84384</t>
+          <t>84170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114997</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39604</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>61487</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87146</t>
+          <t>85366</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106384</t>
+          <t>106102</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137577</t>
+          <t>137342</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>12946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>14352</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20463</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>13353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19988</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40978</t>
+          <t>40428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61978</t>
+          <t>61460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50756</t>
+          <t>50294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76410</t>
+          <t>76807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105136</t>
+          <t>106399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34923</t>
+          <t>35189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>55587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49727</t>
+          <t>49831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>71052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99970</t>
+          <t>99128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54659</t>
+          <t>55023</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77221</t>
+          <t>78220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42662</t>
+          <t>42933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64617</t>
+          <t>65192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103043</t>
+          <t>102081</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>134786</t>
+          <t>133873</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45018</t>
+          <t>44083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42289</t>
+          <t>41929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62675</t>
+          <t>63340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72961</t>
+          <t>72862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100388</t>
+          <t>100264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37927</t>
+          <t>37991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58034</t>
+          <t>57604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43641</t>
+          <t>41909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64540</t>
+          <t>64249</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85506</t>
+          <t>85691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115637</t>
+          <t>117607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16399</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31288</t>
+          <t>31713</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25276</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37600</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27463</t>
+          <t>27558</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25227</t>
+          <t>26521</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42346</t>
+          <t>43120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>18376</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18328</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32882</t>
+          <t>32820</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17484</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31089</t>
+          <t>30399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>27552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45461</t>
+          <t>45220</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>61523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>88199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40377</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63315</t>
+          <t>63405</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108022</t>
+          <t>108640</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141653</t>
+          <t>141586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48387</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73499</t>
+          <t>72062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80762</t>
+          <t>81468</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>110471</t>
+          <t>111458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>143594</t>
+          <t>145195</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79074</t>
+          <t>77774</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>106522</t>
+          <t>104460</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62738</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>89459</t>
+          <t>88763</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>149240</t>
+          <t>148549</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>186544</t>
+          <t>184676</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63980</t>
+          <t>62702</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60490</t>
+          <t>60399</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86967</t>
+          <t>85051</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107044</t>
+          <t>107913</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>141189</t>
+          <t>141249</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80310</t>
+          <t>80557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69260</t>
+          <t>69703</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96743</t>
+          <t>96024</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131453</t>
+          <t>133267</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>167790</t>
+          <t>168721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
